--- a/exports/APLAPOLLO_full_report.xlsx
+++ b/exports/APLAPOLLO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>955</v>
+        <v>909</v>
       </c>
       <c r="I2" t="n">
         <v>914.6072022234555</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>4.14</v>
+        <v>-0.87</v>
       </c>
       <c r="L2" t="n">
-        <v>2.96</v>
+        <v>3.93</v>
       </c>
       <c r="M2" t="n">
-        <v>0.62</v>
+        <v>1.52</v>
       </c>
       <c r="N2" t="n">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="O2" t="n">
         <v>-1.39</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>873.4</v>
+        <v>912.8</v>
       </c>
       <c r="I3" t="n">
         <v>900.8420188610073</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.92</v>
+        <v>-0.42</v>
       </c>
       <c r="L3" t="n">
         <v>6.03</v>
       </c>
       <c r="M3" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="N3" t="n">
         <v>5.99</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.69</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>896</v>
+        <v>825</v>
       </c>
       <c r="I4" t="n">
         <v>835.288964847575</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.84</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>4.77</v>
+        <v>10.93</v>
       </c>
       <c r="M4" t="n">
-        <v>2.22</v>
+        <v>4.69</v>
       </c>
       <c r="N4" t="n">
-        <v>2.61</v>
+        <v>7.88</v>
       </c>
       <c r="O4" t="n">
         <v>5.3</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>12.35</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44623.38541666666</v>
+        <v>44623.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>853.25</v>
+        <v>872</v>
       </c>
       <c r="I5" t="n">
         <v>869.970612349003</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.42</v>
+        <v>-5.7</v>
       </c>
       <c r="L5" t="n">
-        <v>5.21</v>
+        <v>6.04</v>
       </c>
       <c r="M5" t="n">
         <v>1.18</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.93</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>985.55</v>
+        <v>984</v>
       </c>
       <c r="I6" t="n">
         <v>984.3113182667277</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>61.83333333333334</v>
+        <v>62</v>
       </c>
       <c r="K6" t="n">
-        <v>13.02</v>
+        <v>12.84</v>
       </c>
       <c r="L6" t="n">
         <v>6.54</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.82</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>898.5</v>
+        <v>924.8</v>
       </c>
       <c r="I7" t="n">
         <v>924.3329247962686</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>8.69</v>
+        <v>6.02</v>
       </c>
       <c r="L7" t="n">
         <v>3.21</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.33</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44725.38541666666</v>
+        <v>44725.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>924</v>
+        <v>905.95</v>
       </c>
       <c r="I8" t="n">
         <v>919.5034281350726</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.09</v>
+        <v>-2.04</v>
       </c>
       <c r="L8" t="n">
         <v>7.92</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>900</v>
+        <v>932.25</v>
       </c>
       <c r="I9" t="n">
         <v>902.2226198899164</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>0.66</v>
+        <v>-2.9</v>
       </c>
       <c r="L9" t="n">
         <v>4.3</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.85</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44798.38541666666</v>
+        <v>44798.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>1041</v>
+        <v>1024</v>
       </c>
       <c r="I10" t="n">
         <v>1033.604103746367</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>11.67</v>
+        <v>9.84</v>
       </c>
       <c r="L10" t="n">
         <v>5.49</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.6</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44805.38541666666</v>
+        <v>44805.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1002.85</v>
+        <v>1036</v>
       </c>
       <c r="I11" t="n">
         <v>1035.134184431689</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.07</v>
+        <v>-1.17</v>
       </c>
       <c r="L11" t="n">
         <v>2.73</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.26</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1055</v>
+        <v>1044</v>
       </c>
       <c r="I12" t="n">
         <v>1044.490304097646</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>69</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>1.83</v>
+        <v>0.77</v>
       </c>
       <c r="L12" t="n">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="M12" t="n">
         <v>1.87</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.96</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44886.55208333334</v>
+        <v>44887.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1105.1</v>
+        <v>1130</v>
       </c>
       <c r="I13" t="n">
         <v>1116.691808351224</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.85</v>
+        <v>-8.24</v>
       </c>
       <c r="L13" t="n">
-        <v>6.32</v>
+        <v>9.66</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>6.75</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1108</v>
+        <v>1074.3</v>
       </c>
       <c r="I14" t="n">
         <v>1099.633948096169</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.95</v>
+        <v>-4.93</v>
       </c>
       <c r="L14" t="n">
         <v>5.83</v>
       </c>
       <c r="M14" t="n">
-        <v>0.29</v>
+        <v>0.72</v>
       </c>
       <c r="N14" t="n">
         <v>3.96</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.49</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44930.38541666666</v>
+        <v>44930.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1129.6</v>
+        <v>1135</v>
       </c>
       <c r="I15" t="n">
         <v>1131.989123370621</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.15</v>
+        <v>-5.65</v>
       </c>
       <c r="L15" t="n">
         <v>6.3</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44980.55208333334</v>
+        <v>44981.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1259</v>
+        <v>1235.7</v>
       </c>
       <c r="I16" t="n">
         <v>1236.215788273895</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>10.93</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L16" t="n">
         <v>4.59</v>
@@ -1353,7 +1544,7 @@
         <v>0.55</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="O16" t="n">
         <v>4.22</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45069.38541666666</v>
+        <v>45069.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1140.5</v>
+        <v>1156</v>
       </c>
       <c r="I17" t="n">
         <v>1149.885749538783</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>88</v>
+        <v>88.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>7.7</v>
+        <v>6.45</v>
       </c>
       <c r="L17" t="n">
         <v>3.91</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.04</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1537</v>
+        <v>1469.35</v>
       </c>
       <c r="I18" t="n">
         <v>1481.104840754015</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>73</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>32.96</v>
+        <v>27.11</v>
       </c>
       <c r="L18" t="n">
         <v>4.76</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>11.16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45161.55208333334</v>
+        <v>45162.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1590</v>
+        <v>1656.1</v>
       </c>
       <c r="I19" t="n">
         <v>1597.051089137162</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.210000000000001</v>
+        <v>-12.71</v>
       </c>
       <c r="L19" t="n">
-        <v>11.48</v>
+        <v>13.24</v>
       </c>
       <c r="M19" t="n">
         <v>0.76</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>4.52</v>
       </c>
       <c r="O19" t="n">
         <v>-3.9</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1725</v>
+        <v>1628.05</v>
       </c>
       <c r="I20" t="n">
         <v>1661.58202844846</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>4.16</v>
+        <v>-1.69</v>
       </c>
       <c r="L20" t="n">
         <v>3.84</v>
@@ -1581,7 +1820,7 @@
         <v>0.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>5.51</v>
       </c>
       <c r="O20" t="n">
         <v>4.52</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.56</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45202.38541666666</v>
+        <v>45202.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>1620.05</v>
+        <v>1635</v>
       </c>
       <c r="I21" t="n">
         <v>1632.883454545987</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.49</v>
+        <v>-0.43</v>
       </c>
       <c r="L21" t="n">
         <v>7.6</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.03</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1727.95</v>
+        <v>1625</v>
       </c>
       <c r="I22" t="n">
         <v>1671.370398521383</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>5.69</v>
+        <v>-0.61</v>
       </c>
       <c r="L22" t="n">
         <v>4.95</v>
@@ -1695,7 +1958,7 @@
         <v>0.99</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>4.65</v>
       </c>
       <c r="O22" t="n">
         <v>0.19</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.84</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45238.55208333334</v>
+        <v>45239.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1609.5</v>
+        <v>1646.45</v>
       </c>
       <c r="I23" t="n">
         <v>1633.738062534908</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>0.95</v>
+        <v>-1.32</v>
       </c>
       <c r="L23" t="n">
         <v>6.15</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>7.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45264.55208333334</v>
+        <v>45265.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1614.8</v>
+        <v>1591.9</v>
       </c>
       <c r="I24" t="n">
         <v>1612.452299725626</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.92</v>
+        <v>-3.31</v>
       </c>
       <c r="L24" t="n">
-        <v>2.27</v>
+        <v>3.91</v>
       </c>
       <c r="M24" t="n">
         <v>1.22</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.05</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45295.55208333334</v>
+        <v>45296.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1448</v>
+        <v>1547</v>
       </c>
       <c r="I25" t="n">
         <v>1536.295541526609</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K25" t="n">
-        <v>9.039999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="L25" t="n">
         <v>3.34</v>
@@ -1866,7 +2165,7 @@
         <v>1.17</v>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>5.73</v>
       </c>
       <c r="O25" t="n">
         <v>-0.61</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.01</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45323.55208333334</v>
+        <v>45324.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1489.8</v>
+        <v>1475.85</v>
       </c>
       <c r="I26" t="n">
         <v>1480.924585235359</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.7</v>
+        <v>-4.6</v>
       </c>
       <c r="L26" t="n">
         <v>6</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.62</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1418</v>
+        <v>1434.45</v>
       </c>
       <c r="I27" t="n">
         <v>1430.965046693584</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>3.92</v>
+        <v>2.81</v>
       </c>
       <c r="L27" t="n">
         <v>1.49</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1607</v>
+        <v>1485.8</v>
       </c>
       <c r="I28" t="n">
         <v>1516.309470485434</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>12.03</v>
+        <v>3.58</v>
       </c>
       <c r="L28" t="n">
         <v>2.23</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.25</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1569.8</v>
+        <v>1601</v>
       </c>
       <c r="I29" t="n">
         <v>1575.200004209624</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.65</v>
+        <v>-7.75</v>
       </c>
       <c r="L29" t="n">
-        <v>8.220000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>1.64</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.69</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45440.55208333334</v>
+        <v>45441.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1617.95</v>
+        <v>1608.9</v>
       </c>
       <c r="I30" t="n">
         <v>1613.987161848348</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>1.06</v>
+        <v>0.49</v>
       </c>
       <c r="L30" t="n">
         <v>10.12</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>6.75</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1614.35</v>
+        <v>1648.4</v>
       </c>
       <c r="I31" t="n">
         <v>1624.658662327143</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.34</v>
+        <v>-2.46</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>3.64</v>
       </c>
       <c r="M31" t="n">
         <v>4.62</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>10.01</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1528</v>
+        <v>1509.95</v>
       </c>
       <c r="I32" t="n">
         <v>1512.072834550011</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.3</v>
+        <v>-8.4</v>
       </c>
       <c r="L32" t="n">
-        <v>8.4</v>
+        <v>9.43</v>
       </c>
       <c r="M32" t="n">
         <v>1.42</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.33</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45531.38541666666</v>
+        <v>45531.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1422.6</v>
+        <v>1440</v>
       </c>
       <c r="I33" t="n">
         <v>1430.904062918356</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>5.78</v>
+        <v>4.63</v>
       </c>
       <c r="L33" t="n">
         <v>1.04</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45541.38541666666</v>
+        <v>45541.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1432</v>
+        <v>1414</v>
       </c>
       <c r="I34" t="n">
         <v>1422.293209838344</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.81</v>
       </c>
       <c r="L34" t="n">
-        <v>1.7</v>
+        <v>3.19</v>
       </c>
       <c r="M34" t="n">
         <v>0.75</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.18</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1478.95</v>
+        <v>1505.75</v>
       </c>
       <c r="I35" t="n">
         <v>1491.230662189779</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.59</v>
+        <v>-6.49</v>
       </c>
       <c r="L35" t="n">
-        <v>5.12</v>
+        <v>7.43</v>
       </c>
       <c r="M35" t="n">
         <v>1.17</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.05</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1540.25</v>
+        <v>1523.95</v>
       </c>
       <c r="I36" t="n">
         <v>1527.406324099024</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K36" t="n">
-        <v>2.29</v>
+        <v>1.21</v>
       </c>
       <c r="L36" t="n">
         <v>1.78</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.15</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45624.55208333334</v>
+        <v>45625.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1469.2</v>
+        <v>1539.75</v>
       </c>
       <c r="I37" t="n">
         <v>1521.356583437897</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K37" t="n">
-        <v>3.59</v>
+        <v>-1.04</v>
       </c>
       <c r="L37" t="n">
         <v>2.15</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.75</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45649.55208333334</v>
+        <v>45650.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1538.5</v>
+        <v>1513.15</v>
       </c>
       <c r="I38" t="n">
         <v>1530.590256967731</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.08</v>
+        <v>-1.73</v>
       </c>
       <c r="L38" t="n">
         <v>6.14</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.74</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45656.55208333334</v>
+        <v>45657.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1518</v>
+        <v>1572.95</v>
       </c>
       <c r="I39" t="n">
         <v>1572.872506469804</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.32</v>
+        <v>-3.95</v>
       </c>
       <c r="L39" t="n">
-        <v>1.87</v>
+        <v>4.42</v>
       </c>
       <c r="M39" t="n">
         <v>0.35</v>
       </c>
       <c r="N39" t="n">
-        <v>0.75</v>
+        <v>3.44</v>
       </c>
       <c r="O39" t="n">
         <v>-1.62</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45667.38541666666</v>
+        <v>45667.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1532.3</v>
+        <v>1515.05</v>
       </c>
       <c r="I40" t="n">
         <v>1527.030711789147</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.58</v>
+        <v>-3.68</v>
       </c>
       <c r="L40" t="n">
         <v>4.54</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>6.5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1510</v>
+        <v>1530.9</v>
       </c>
       <c r="I41" t="n">
         <v>1527.960239884929</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>0.33</v>
+        <v>-1.05</v>
       </c>
       <c r="L41" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="M41" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="N41" t="n">
         <v>3.15</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.35</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45684.55208333334</v>
+        <v>45685.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1509</v>
+        <v>1470.9</v>
       </c>
       <c r="I42" t="n">
         <v>1480.247179857471</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.43</v>
+        <v>-3.92</v>
       </c>
       <c r="L42" t="n">
-        <v>2.11</v>
+        <v>5.15</v>
       </c>
       <c r="M42" t="n">
         <v>2.08</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1384.85</v>
+        <v>1450.5</v>
       </c>
       <c r="I43" t="n">
         <v>1419.183729477455</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>5.85</v>
+        <v>1.39</v>
       </c>
       <c r="L43" t="n">
         <v>4.39</v>
@@ -2892,7 +3407,7 @@
         <v>0.84</v>
       </c>
       <c r="N43" t="n">
-        <v>5.27</v>
+        <v>6.4</v>
       </c>
       <c r="O43" t="n">
         <v>-1.26</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>11.28</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45729.38541666666</v>
+        <v>45729.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1381.4</v>
+        <v>1367</v>
       </c>
       <c r="I44" t="n">
         <v>1372.403274387945</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.76</v>
+        <v>-5.76</v>
       </c>
       <c r="L44" t="n">
-        <v>5.29</v>
+        <v>5.89</v>
       </c>
       <c r="M44" t="n">
         <v>1.4</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.09</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45735.38541666666</v>
+        <v>45735.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>1473.15</v>
+        <v>1489.05</v>
       </c>
       <c r="I45" t="n">
         <v>1477.654389002517</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.77</v>
+        <v>-8.93</v>
       </c>
       <c r="L45" t="n">
-        <v>8.119999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="M45" t="n">
         <v>2.05</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.13</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1518.05</v>
+        <v>1413.75</v>
       </c>
       <c r="I46" t="n">
         <v>1479.510750775456</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>1.95</v>
+        <v>-5.06</v>
       </c>
       <c r="L46" t="n">
-        <v>1.22</v>
+        <v>5.98</v>
       </c>
       <c r="M46" t="n">
-        <v>0.19</v>
+        <v>1.19</v>
       </c>
       <c r="N46" t="n">
-        <v>3.19</v>
+        <v>4.89</v>
       </c>
       <c r="O46" t="n">
         <v>4.13</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>10.95</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1518</v>
+        <v>1550</v>
       </c>
       <c r="I47" t="n">
         <v>1545.362546416224</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.37</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>8.44</v>
+        <v>10.69</v>
       </c>
       <c r="M47" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="N47" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="O47" t="n">
         <v>-4.89</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1840.4</v>
+        <v>1834.2</v>
       </c>
       <c r="I48" t="n">
         <v>1835.572226004922</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K48" t="n">
-        <v>18.74</v>
+        <v>18.34</v>
       </c>
       <c r="L48" t="n">
         <v>2.4</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.44</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1585.9</v>
+        <v>1616.1</v>
       </c>
       <c r="I49" t="n">
         <v>1606.988549679363</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K49" t="n">
-        <v>13.54</v>
+        <v>11.89</v>
       </c>
       <c r="L49" t="n">
         <v>1.86</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.18</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45980.38541666666</v>
+        <v>45980.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1744.8</v>
+        <v>1717</v>
       </c>
       <c r="I50" t="n">
         <v>1738.393628555924</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>106</v>
+        <v>106.1666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>7.96</v>
+        <v>6.24</v>
       </c>
       <c r="L50" t="n">
         <v>4.15</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.64</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45994.55208333334</v>
+        <v>45995.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1757</v>
+        <v>1761.9</v>
       </c>
       <c r="I51" t="n">
         <v>1760.548125851045</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.33</v>
+        <v>-2.62</v>
       </c>
       <c r="L51" t="n">
-        <v>2.33</v>
+        <v>3.08</v>
       </c>
       <c r="M51" t="n">
         <v>0.76</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>3.63</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1893.3</v>
+        <v>1873.6</v>
       </c>
       <c r="I52" t="n">
         <v>1891.894539669068</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K52" t="n">
-        <v>7.46</v>
+        <v>6.34</v>
       </c>
       <c r="L52" t="n">
         <v>2.91</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.51</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46044.38541666666</v>
+        <v>46044.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1938.9</v>
+        <v>1981.2</v>
       </c>
       <c r="I53" t="n">
         <v>1958.008748948595</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.49</v>
+        <v>-5.74</v>
       </c>
       <c r="L53" t="n">
-        <v>4.87</v>
+        <v>5.89</v>
       </c>
       <c r="M53" t="n">
         <v>1.44</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.19</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46073.38541666666</v>
+        <v>46073.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>2203.5</v>
+        <v>2180</v>
       </c>
       <c r="I54" t="n">
         <v>2181.502227186363</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K54" t="n">
-        <v>11.22</v>
+        <v>10.03</v>
       </c>
       <c r="L54" t="n">
         <v>2.42</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.67</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1896.9</v>
+        <v>2033.9</v>
       </c>
       <c r="I55" t="n">
         <v>2033.700994924299</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>12.99</v>
+        <v>6.7</v>
       </c>
       <c r="L55" t="n">
         <v>3.33</v>
       </c>
       <c r="M55" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="N55" t="n">
-        <v>4.86</v>
+        <v>8.1</v>
       </c>
       <c r="O55" t="n">
         <v>-0.63</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.25</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2028.8</v>
+        <v>2009.3</v>
       </c>
       <c r="I56" t="n">
         <v>2010.424479994198</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.25</v>
+        <v>-1.21</v>
       </c>
       <c r="L56" t="n">
         <v>3.58</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.75</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1842.7</v>
+        <v>1857.5</v>
       </c>
       <c r="I57" t="n">
         <v>1848.976701452659</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>54</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="K57" t="n">
-        <v>8.289999999999999</v>
+        <v>7.55</v>
       </c>
       <c r="L57" t="n">
         <v>2.03</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>5.45</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46202.55208333334</v>
+        <v>46203.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1789.1</v>
+        <v>1787.7</v>
       </c>
       <c r="I58" t="n">
         <v>1788.244542051907</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.68</v>
+        <v>-3.76</v>
       </c>
       <c r="L58" t="n">
-        <v>4.18</v>
+        <v>4.81</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="N58" t="n">
         <v>1.48</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>3.74</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1825</v>
+        <v>1852.3</v>
       </c>
       <c r="I59" t="n">
         <v>1851.789836639743</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.09</v>
+        <v>-3.61</v>
       </c>
       <c r="L59" t="n">
-        <v>3.35</v>
+        <v>4.27</v>
       </c>
       <c r="M59" t="n">
         <v>1.17</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>4.2</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46234.38541666666</v>
+        <v>46234.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1868.5</v>
+        <v>1808</v>
       </c>
       <c r="I60" t="n">
         <v>1824.171802234846</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>0.87</v>
+        <v>-2.39</v>
       </c>
       <c r="L60" t="n">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="M60" t="n">
         <v>-0</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.38</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46237.38541666666</v>
+        <v>46237.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1907.9</v>
+        <v>1947</v>
       </c>
       <c r="I61" t="n">
         <v>1923.331340189775</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.53</v>
+        <v>-7.69</v>
       </c>
       <c r="L61" t="n">
         <v>8.300000000000001</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.66</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46267.55208333334</v>
+        <v>46268.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2218</v>
+        <v>2154.9</v>
       </c>
       <c r="I62" t="n">
         <v>2158.85220479575</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>13.92</v>
+        <v>10.68</v>
       </c>
       <c r="L62" t="n">
         <v>2.5</v>
@@ -3975,7 +4718,7 @@
         <v>0.6</v>
       </c>
       <c r="N62" t="n">
-        <v>1.24</v>
+        <v>2.89</v>
       </c>
       <c r="O62" t="n">
         <v>7.69</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.98</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>2073.8</v>
+        <v>2203.3</v>
       </c>
       <c r="I63" t="n">
         <v>2145.005187519904</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K63" t="n">
-        <v>3.76</v>
+        <v>-2.25</v>
       </c>
       <c r="L63" t="n">
         <v>5.85</v>
       </c>
       <c r="M63" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="N63" t="n">
-        <v>4.32</v>
+        <v>5.95</v>
       </c>
       <c r="O63" t="n">
         <v>-2.89</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4092,6 +4859,12 @@
       <c r="Q64" t="n">
         <v>2</v>
       </c>
+      <c r="R64" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6194,7 +6967,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="6">
@@ -6204,7 +6977,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7">
@@ -6214,7 +6987,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="8">
@@ -6224,7 +6997,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6234,7 +7007,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.1</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="10">
@@ -6244,7 +7017,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="11">
@@ -6254,7 +7027,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -6264,7 +7037,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6274,7 +7047,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.40000000000001</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
@@ -6284,7 +7057,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="15">
@@ -6294,7 +7067,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.25</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="16">
@@ -6304,7 +7077,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.95</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="17">
@@ -6314,7 +7087,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.96</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="18">
@@ -6324,7 +7097,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="19">
@@ -6334,7 +7107,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.4</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="20">
@@ -6344,7 +7117,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.16</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="21">
@@ -6354,7 +7127,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.48</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="22">
@@ -6364,7 +7137,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -6374,7 +7147,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6384,7 +7157,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="25">
@@ -6404,7 +7177,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.89</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="27">
@@ -6424,7 +7197,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
